--- a/public/deviceExcel/airConditoner.xlsx
+++ b/public/deviceExcel/airConditoner.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>园区名称</t>
+  </si>
+  <si>
+    <t>安装地址</t>
   </si>
   <si>
     <t>空调型号</t>
@@ -37,6 +40,10 @@
   <si>
     <t>空调类型
 （分体式空调/多联机空调外机/中央空调面板）</t>
+  </si>
+  <si>
+    <t>数据来源
+（本地/天创达）</t>
   </si>
   <si>
     <t>空调名称</t>
@@ -49,9 +56,6 @@
   </si>
   <si>
     <t>计量设备编号</t>
-  </si>
-  <si>
-    <t>安装地址</t>
   </si>
   <si>
     <t>备注</t>
@@ -67,7 +71,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,20 +88,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -550,19 +540,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -571,127 +570,118 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -707,7 +697,7 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,46 +1048,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.0909090909091" customWidth="1"/>
-    <col min="2" max="2" width="10.6363636363636" style="1" customWidth="1"/>
-    <col min="3" max="3" width="43.2727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3636363636364" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.1818181818182" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7272727272727" style="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6363636363636" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9.81818181818182" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.81818181818182" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6363636363636" style="1" customWidth="1"/>
+    <col min="4" max="4" width="43.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7272727272727" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10.3636363636364" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.1818181818182" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7272727272727" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.6363636363636" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1" spans="1:9">
+    <row r="1" ht="34" customHeight="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
